--- a/packages/docsluice/test/readers/xlsx/fixtures/headers_comments_hidden_tables_defined_names.xlsx
+++ b/packages/docsluice/test/readers/xlsx/fixtures/headers_comments_hidden_tables_defined_names.xlsx
@@ -16,6 +16,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Fixture Author</author>
+    <author>Unreferenced Author</author>
   </authors>
   <commentList>
     <comment ref="A2" authorId="0">
